--- a/data/trans_dic/P25C$pormicuenta_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25C$pormicuenta_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue sin ayuda específica</t>
+          <t>Población cuyo método para dejar de fumar fue sin ayuda específica (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,49; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,17; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,58; 93,64</t>
+          <t>40,02; 93,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,2; 100,0</t>
+          <t>80,12; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,57; 95,63</t>
+          <t>73,26; 97,1</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,69; 96,28</t>
+          <t>69,74; 95,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,22; 96,4</t>
+          <t>81,58; 96,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,53; 94,32</t>
+          <t>80,07; 94,25</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,37; 100,0</t>
+          <t>90,48; 99,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,71; 94,7</t>
+          <t>85,38; 94,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,12; 99,02</t>
+          <t>90,56; 99,29</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>78,85; 89,77</t>
+          <t>78,08; 89,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,93; 90,82</t>
+          <t>79,68; 91,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,49; 88,74</t>
+          <t>80,53; 88,92</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86,5; 94,4</t>
+          <t>86,32; 94,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,65; 94,06</t>
+          <t>79,51; 93,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85,97; 92,99</t>
+          <t>86,04; 93,19</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>90,45; 97,38</t>
+          <t>90,64; 97,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>75,53; 96,86</t>
+          <t>75,94; 97,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90,72; 96,91</t>
+          <t>90,6; 96,83</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>88,68; 97,0</t>
+          <t>88,66; 97,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,33; 92,45</t>
+          <t>87,16; 92,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,13; 95,92</t>
+          <t>89,04; 95,7</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue sin ayuda específica</t>
+          <t>Población cuyo método para dejar de fumar fue sin ayuda específica (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4260; 7663</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15645; 18299</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22890; 25961</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8795; 19343</t>
+          <t>8268; 19398</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25408; 30539</t>
+          <t>24467; 30539</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36128; 48960</t>
+          <t>37507; 49712</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31787; 43297</t>
+          <t>31362; 42939</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42921; 50324</t>
+          <t>42588; 50136</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78254; 91658</t>
+          <t>77811; 91586</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>313694; 347127</t>
+          <t>314087; 346703</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73793; 82491</t>
+          <t>74370; 82680</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>391343; 429979</t>
+          <t>393244; 431172</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>123697; 140827</t>
+          <t>122491; 140257</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68036; 78289</t>
+          <t>68685; 78541</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195665; 215708</t>
+          <t>195753; 216133</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>134505; 146796</t>
+          <t>134232; 146319</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36177; 42721</t>
+          <t>36115; 42666</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>172725; 186839</t>
+          <t>172871; 187233</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>105611; 113698</t>
+          <t>105829; 113638</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13349; 17120</t>
+          <t>13423; 17217</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121956; 130279</t>
+          <t>121795; 130168</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>753362; 824064</t>
+          <t>753183; 824349</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>294702; 311951</t>
+          <t>294116; 311532</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1058013; 1138617</t>
+          <t>1056936; 1136007</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$pormicuenta_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25C$pormicuenta_2023-Edad-trans_dic.xlsx
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>89,17%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,02; 93,9</t>
+          <t>47,6; 94,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,12; 100,0</t>
+          <t>80,87; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,26; 97,1</t>
+          <t>74,49; 97,28</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69,74; 95,48</t>
+          <t>71,1; 95,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,58; 96,04</t>
+          <t>82,36; 96,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,07; 94,25</t>
+          <t>81,12; 94,61</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,48; 99,88</t>
+          <t>84,41; 96,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,38; 94,92</t>
+          <t>84,99; 94,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,56; 99,29</t>
+          <t>86,3; 94,4</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,18%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>78,08; 89,4</t>
+          <t>78,67; 89,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,68; 91,12</t>
+          <t>80,05; 91,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,53; 88,92</t>
+          <t>80,87; 88,72</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86,32; 94,1</t>
+          <t>85,82; 93,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,51; 93,94</t>
+          <t>78,65; 93,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,04; 93,19</t>
+          <t>85,77; 92,78</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>90,64; 97,33</t>
+          <t>90,46; 97,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>75,94; 97,41</t>
+          <t>74,88; 97,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90,6; 96,83</t>
+          <t>90,12; 96,82</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>88,66; 97,03</t>
+          <t>86,52; 91,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,16; 92,32</t>
+          <t>87,7; 92,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,04; 95,7</t>
+          <t>87,84; 91,47</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26745</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>20336</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>29449</t>
+          <t>32988</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45040</t>
+          <t>53323</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8268; 19398</t>
+          <t>12249; 24432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24467; 30539</t>
+          <t>27553; 34069</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37507; 49712</t>
+          <t>44548; 58175</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39103</t>
+          <t>43050</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47441</t>
+          <t>51312</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86544</t>
+          <t>94362</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31362; 42939</t>
+          <t>35041; 46960</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42588; 50136</t>
+          <t>46534; 54370</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77811; 91586</t>
+          <t>85810; 100078</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>338870</t>
+          <t>103920</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>79198</t>
+          <t>83891</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>418068</t>
+          <t>187811</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>314087; 346703</t>
+          <t>95720; 109172</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74370; 82680</t>
+          <t>78599; 87848</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>393244; 431172</t>
+          <t>177663; 194350</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>132856</t>
+          <t>139599</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74026</t>
+          <t>81364</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206882</t>
+          <t>220963</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>122491; 140257</t>
+          <t>129871; 147733</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68685; 78541</t>
+          <t>75507; 86202</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195753; 216133</t>
+          <t>209790; 230143</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>141129</t>
+          <t>155344</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>40008</t>
+          <t>42749</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181138</t>
+          <t>198093</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>134232; 146319</t>
+          <t>147271; 161090</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36115; 42666</t>
+          <t>38220; 45546</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>172871; 187233</t>
+          <t>188861; 204298</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>110827</t>
+          <t>121940</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>17617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>126601</t>
+          <t>139558</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>105829; 113638</t>
+          <t>116390; 125622</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13423; 17217</t>
+          <t>14704; 19133</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121795; 130168</t>
+          <t>133641; 143576</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>786038</t>
+          <t>590654</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>330202</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1090232</t>
+          <t>920856</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>753183; 824349</t>
+          <t>571253; 605462</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>294116; 311532</t>
+          <t>320890; 339402</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1056936; 1136007</t>
+          <t>901378; 938614</t>
         </is>
       </c>
     </row>
